--- a/backend/data/financials_by_company/000690.SZ.xlsx
+++ b/backend/data/financials_by_company/000690.SZ.xlsx
@@ -3219,7 +3219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3250,730 +3250,750 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fax</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>website</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>industryKey</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>industryDisp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>sectorKey</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>sectorDisp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>longBusinessSummary</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>fullTimeEmployees</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>companyOfficers</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>executiveTeam</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>maxAge</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>previousClose</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>dayLow</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>dayHigh</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>regularMarketPreviousClose</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>regularMarketOpen</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>regularMarketDayLow</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>regularMarketDayHigh</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dividendRate</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>dividendYield</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>exDividendDate</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>payoutRatio</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>fiveYearAvgDividendYield</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>targetHighPrice</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>targetLowPrice</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>targetMeanPrice</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>targetMedianPrice</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4007,506 +4027,524 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>86 75 3251 1298</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>86 75 3251 1398</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>https://www.baolihua.com.cn</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>utilities-independent-power-producers</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>utilities</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Guangdong Baolihua New Energy Stock Co., Ltd. engages in the power and finance business in China. It operates through Management Headquarters; New Energy Power; and Financial Services segments. The company generates and sells power using thermal power and wind sources. It also provides investment and asset management services. Guangdong Baolihua New Energy Stock Co., Ltd. was founded in 1997 and is based in Meixian, China.</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Guangdong Baolihua New Energy Stock Co., Ltd. engages in the energy power and finance investment business in China. It operates through Management Headquarters; New Energy Power; and Financial Services segments. The company generates and sells power using thermal power and wind sources. Guangdong Baolihua New Energy Stock Co., Ltd. was founded in 1997 and is based in Meixian, China.</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>1273</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Mr. Lin  Ye', 'age': 39, 'title': 'GM &amp; Director', 'yearBorn': 1986, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhuowen  Jiang', 'age': 43, 'title': 'Non-Independent Director, Secretary &amp; CFO', 'yearBorn': 1982, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>86400</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.14</v>
-      </c>
       <c r="T2" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>4.97</v>
+        <v>4.73</v>
       </c>
       <c r="V2" t="n">
-        <v>5.14</v>
+        <v>4.84</v>
       </c>
       <c r="W2" t="n">
-        <v>5.14</v>
+        <v>4.68</v>
       </c>
       <c r="X2" t="n">
-        <v>5.4</v>
+        <v>4.76</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.97</v>
+        <v>4.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.14</v>
+        <v>4.84</v>
       </c>
       <c r="AA2" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.4</v>
       </c>
-      <c r="AB2" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1779408000</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.4255</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>2.35</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.893617</v>
-      </c>
       <c r="AH2" t="n">
-        <v>9.481481</v>
+        <v>0.509</v>
       </c>
       <c r="AI2" t="n">
-        <v>85927673</v>
+        <v>9.978724</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85927673</v>
+        <v>8.6851845</v>
       </c>
       <c r="AK2" t="n">
-        <v>155728990</v>
+        <v>48674025</v>
       </c>
       <c r="AL2" t="n">
-        <v>114247257</v>
+        <v>48674025</v>
       </c>
       <c r="AM2" t="n">
-        <v>114247257</v>
+        <v>129183870</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.11</v>
+        <v>70516060</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.12</v>
+        <v>70516060</v>
       </c>
       <c r="AP2" t="n">
-        <v>11140545536</v>
+        <v>4.68</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11184063610</v>
+        <v>4.69</v>
       </c>
       <c r="AR2" t="n">
+        <v>10204914688</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10444261737</v>
+      </c>
+      <c r="AT2" t="n">
         <v>4.18</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AU2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
         <v>18.2</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AW2" t="n">
         <v>0.474687</v>
       </c>
-      <c r="AV2" t="n">
-        <v>1.2729236</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.3756</v>
-      </c>
       <c r="AX2" t="n">
-        <v>4.78295</v>
+        <v>1.166018</v>
       </c>
       <c r="AY2" t="n">
+        <v>5.3732</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.7935</v>
+      </c>
+      <c r="BA2" t="n">
         <v>0.25</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>0.048638135</v>
-      </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>0.05285412</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="BB2" t="b">
+      <c r="BD2" t="b">
         <v>0</v>
       </c>
-      <c r="BC2" t="n">
-        <v>13306574848</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
+        <v>12370942976</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.11823</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BG2" t="n">
         <v>1769975981</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BH2" t="n">
         <v>2175887862</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BI2" t="n">
         <v>0.23319</v>
       </c>
-      <c r="BH2" t="n">
-        <v>0.07787000400000001</v>
-      </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
+        <v>0.051810004</v>
+      </c>
+      <c r="BK2" t="n">
         <v>2175887862</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BL2" t="n">
         <v>6.016</v>
       </c>
-      <c r="BK2" t="n">
-        <v>0.85106385</v>
-      </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
+        <v>0.7795878000000001</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BO2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BP2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BQ2" t="n">
         <v>0.034</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BR2" t="n">
         <v>1034769536</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BS2" t="n">
         <v>0.47</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BT2" t="n">
         <v>0.54</v>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="BV2" t="n">
         <v>1268956800</v>
       </c>
-      <c r="BU2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>6.994</v>
-      </c>
       <c r="BW2" t="n">
-        <v>0.1898148</v>
+        <v>1.414</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.24487448</v>
+        <v>6.502</v>
       </c>
       <c r="BY2" t="n">
+        <v>0.015021443</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.20116603</v>
+      </c>
+      <c r="CA2" t="n">
         <v>0.2</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CB2" t="n">
         <v>1779408000</v>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CB2" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>8.539999999999999</v>
-      </c>
       <c r="CD2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="CE2" t="n">
         <v>6.43</v>
       </c>
-      <c r="CE2" t="n">
-        <v>7.485</v>
-      </c>
       <c r="CF2" t="n">
-        <v>7.485</v>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+        <v>6.43</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>6.43</v>
       </c>
       <c r="CH2" t="n">
-        <v>2</v>
+        <v>6.43</v>
       </c>
       <c r="CI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>strong_buy</t>
+        </is>
+      </c>
+      <c r="CK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL2" t="n">
         <v>4782021120</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CM2" t="n">
         <v>2.198</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CN2" t="n">
         <v>1902638208</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CO2" t="n">
         <v>6948049920</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CP2" t="n">
         <v>1.731</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CQ2" t="n">
         <v>1.977</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CR2" t="n">
         <v>8751935488</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CS2" t="n">
         <v>53.081</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CT2" t="n">
         <v>3.989</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CU2" t="n">
         <v>0.03878</v>
       </c>
-      <c r="CS2" t="n">
+      <c r="CV2" t="n">
         <v>0.08091</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CW2" t="n">
         <v>1697910784</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CX2" t="n">
         <v>754657472</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CY2" t="n">
         <v>2031334784</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CZ2" t="n">
         <v>0</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="DA2" t="n">
         <v>0.06</v>
       </c>
-      <c r="CY2" t="n">
+      <c r="DB2" t="n">
         <v>0.19399999</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DC2" t="n">
         <v>0.2174</v>
       </c>
-      <c r="DA2" t="n">
+      <c r="DD2" t="n">
         <v>0.20583999</v>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>000690.SZ</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DH2" t="b">
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>-0.01999998</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>4.97 - 5.14</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DM2" t="n">
+        <v>-0.6831999</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.12714954</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.10349989</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.021591716</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>1.0 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>finmb_9734979</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.8456650999999999</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>GUANGDONG BAOLIHUA NEW ENERGY S</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Guangdong Baolihua New Energy Stock Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>1783062297</v>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>854415000000</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.03999996</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>4.68 - 4.76</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>GUANGDONG BAOLIHUA NEW ENERGY S</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Guangdong Baolihua New Energy Stock Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>155728990</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.94000006</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.22488041</v>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EN2" t="n">
+        <v>129183870</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.5100002</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.12200963</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>4.18 - 6.4</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>-1.2800002</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.20000003</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>18.98148</v>
-      </c>
-      <c r="DV2" t="n">
+      <c r="ER2" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-0.2671875</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1.5021443</v>
+      </c>
+      <c r="EU2" t="n">
         <v>1666349940</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EV2" t="n">
         <v>1666612800</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EW2" t="n">
         <v>0.47</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EX2" t="n">
         <v>0.54</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>-0.25559998</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.04754818</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.33704996</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.07046905000000001</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1782111885</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.38910472</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>finmb_9734979</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="ER2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>854415000000</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="EY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
